--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R3d7059dab8f74b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R7fe6f192e2924946"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -540,7 +540,7 @@
         <x:v>完成条件</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
-        <x:v>npm run compile:push返回0，五个目标路径可读，四份报告以template_id、locale和job_id闭合</x:v>
+        <x:v>npm run compile:push返回0，Prompt声明的目标路径可读，业务报告以template_id、locale和job_id闭合</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R7fe6f192e2924946"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Ra63aecc015d142d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -452,15 +452,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="23" t="str">
-        <x:v>脱敏推送发布演练中的模板库、国际化策略和发送队列</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
+        <x:v>本次推送发布的模板库、国际化策略和发送队列，用户标识已经脱敏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="33" customHeight="1">
       <x:c r="A6" s="22" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
-        <x:v>解压输入数据包后在input_data目录读取templates、rules、data和starter</x:v>
+        <x:v>在推送发布前发现地区模板合同和回退问题，给发布值班提供逐条发送裁决及最终文案</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
@@ -481,10 +481,10 @@
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="22" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="23" t="str">
-        <x:v>读取模板与策略；解析变量合同；比较地区差异；展开地区矩阵；执行回退；裁决发送队列；渲染ready任务；输出业务报告</x:v>
+        <x:v>用Node.js读取模板与策略，解析变量合同并比较地区差异，展开地区矩阵后执行回退、裁决发送队列、渲染ready任务并输出报告</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -529,34 +529,34 @@
     </x:row>
     <x:row r="15" ht="33" customHeight="1">
       <x:c r="A15" s="22" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B15" s="23" t="str">
-        <x:v>正式处理只读取本地模板、策略和队列，不修改业务输入，不连接外部服务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" customHeight="1">
+        <x:v>只读取随包模板、策略和发送队列，不修改输入文件，也不连接外部服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="22" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B16" s="23" t="str">
-        <x:v>npm run compile:push返回0，Prompt声明的目标路径可读，业务报告以template_id、locale和job_id闭合</x:v>
+        <x:v>交付完成版编译程序和四份CSV，业务报告以template_id、locale和job_id闭合</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="22" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对</x:v>
       </x:c>
       <x:c r="B17" s="23" t="str">
-        <x:v>变量集合、消息部件、回退首选地区、路径、合同状态、原因顺序、ready集合、复数分支、HTML转义、来源和排序</x:v>
+        <x:v>核对变量集合、消息部件、回退地区与路径、合同状态、原因顺序、ready集合、复数分支、HTML转义、来源和排序</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
       <x:c r="A18" s="24" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>允许变体</x:v>
       </x:c>
       <x:c r="B18" s="25" t="str">
-        <x:v>函数拆分、变量名、注释、内部对象、临时数组、CSV必要引号及LF或CRLF行尾</x:v>
+        <x:v>函数拆分、变量名、注释和内部对象可以不同；CSV可使用必要引号以及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
